--- a/series_data/drowned-history/series_log.xlsx
+++ b/series_data/drowned-history/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -817,6 +817,281 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-04 21:32</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/53427c5a8fa41fd96fc1f18e9022531d_1783200698.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-04 21:36</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7031edcf127df94ec07bb9447e1bc803_1783200955.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-04 21:42</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cae99debb4b39e700c3d87668764609e_1783201343.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-04 21:50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/2125d50f0813462b2c5c4b849c5e8ffb.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep02/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-04 21:52</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/db772160c641459c473837b1b201b32b_1783201943.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep02/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/drowned-history/series_log.xlsx
+++ b/series_data/drowned-history/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,6 +1092,281 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-05 21:38</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ff5112713b8f7b439c68c1b944a60ad7_1783287466.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-05 21:43</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9be5fff29649f73c70dc33c92ac220c5_1783287754.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-05 21:46</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/75af4fc4ba2c2f8f4c1ad21633479338_1783287938.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-05 21:49</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0d9585891f1480b669b1573c23a7bbd4_1783288132.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep03/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-05 21:54</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cf425f118e8d89b40004e701f39c09ac_1783288410.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep03/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/drowned-history/series_log.xlsx
+++ b/series_data/drowned-history/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,281 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-06 22:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/575aabecf70f0992e38113c710c4dd91_1783375199.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-06 22:02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f724bb15cebb387d60a760cc0a1bd8be_1783375346.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-06 22:05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9173d9807ea85ffba6bce4f74456b030_1783375485.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-06 22:08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9825af53ecea42806e864f3ddf5fce64_1783375663.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-06 22:10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d366d30b6bb1f77c9f048dca4e3a540e_1783375808.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep04/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/drowned-history/series_log.xlsx
+++ b/series_data/drowned-history/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1642,6 +1642,269 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-07 22:06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/dd646dde311b3ddb0c384237a1192f61_1783461972.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-07 22:45</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-07 23:01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8868d56f0ef86e5ccde7a92bf2c93136_1783465256.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-07 23:03</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f72674b40be47eab7317f0d222ce8d36_1783465395.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-07 23:06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d041e760db17142dd12cc8bc2e5c3e94_1783465563.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep05/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/drowned-history/series_log.xlsx
+++ b/series_data/drowned-history/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1905,6 +1905,245 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-08 21:43</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8e60690478cce6ad92a073c2b572e942_1783546954.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-08 21:45</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9352ca18d9722330fbe261cf94487765_1783547115.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-08 21:49</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-08 21:53</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-08 21:57</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep06/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/drowned-history/series_log.xlsx
+++ b/series_data/drowned-history/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2144,6 +2144,281 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-09 21:59</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/40bc1a476a4bcbea520472b92e9a3bd6_1783634363.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/26cc39f0198053066bead3ea5d2d643f_1783634511.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:05</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f4d0dd12713bc6a92582b745cc655ca1_1783634709.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/72230d1864ce0c3121f540c52163dda4_1783634976.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep07/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0c021c459196f3c513501d7661f007da_1783635103.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep07/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/drowned-history/series_log.xlsx
+++ b/series_data/drowned-history/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2419,6 +2419,281 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-10 21:38</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e2656e2030b05fcf7e8af18ccb736b6c_1783719474.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-10 21:40</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8473e4346b1bdabdca78c0fbe76c6cf3_1783719611.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-10 21:43</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c47a9b999bd87c439053de01cd39eb1c_1783719754.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-10 21:45</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fac078ec95e81fd1cef865219759f15f_1783719895.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-10 21:47</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bb18a41f7897c310c6d4a133f001a4df_1783720029.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep08/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/drowned-history/series_log.xlsx
+++ b/series_data/drowned-history/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2694,6 +2694,281 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-11 21:25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/cb1a1781e89bed05e5f5cd993bcb229f.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-11 21:27</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5c87343817bc59fe2a03cd48366209c9_1783805217.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep09/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-11 21:29</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/308269738c8d9ebc43c3a0b9896d5840_1783805343.mp4</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep09/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-11 21:31</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/998bdfc375c64bd1c204c05d9eef5c86_1783805460.mp4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep09/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-11 21:33</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d585f35721ba7dfc03a28f3021db163a_1783805602.mp4</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep09/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/drowned-history/series_log.xlsx
+++ b/series_data/drowned-history/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2969,6 +2969,281 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-12 21:25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cd5e71878a023e4c92767f5b5fffe318_1783891479.mp4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-12 21:27</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e9eaec1534a8e0b67657a85f475af728_1783891616.mp4</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep10/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-12 21:30</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/37d82aefa072df6bc120dff38afd1f61.mp4</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep10/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-12 21:32</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8d955b8bd7f536bc51c0d80fa6eb828a_1783891911.mp4</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep10/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-12 21:35</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/430628042dbf2f35e75b953918beb244.mp4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep10/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/drowned-history/series_log.xlsx
+++ b/series_data/drowned-history/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3244,6 +3244,281 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:31</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/612a582bf81597d8f056af5807c99ee9_1783978234.mp4</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep11/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:34</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d22eccabb240581372e1c70392a9a7f5_1783978423.mp4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep11/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:36</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b5af3f25bf2441db4823d263b7d0e1d9_1783978558.mp4</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep11/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:39</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/95cb33e823dfe1b6363efd9e699fa3b4_1783978724.mp4</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep11/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:42</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e37a25222677658a6cb955ea85fbfd31_1783978890.mp4</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/drowned-history/episodes/ep11/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
